--- a/data/trans_orig/Predimed_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según adherencia a la dieta mediterránea en 2023</t>
+          <t>Población según adherencia a la dieta mediterránea en 2023 (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61775</t>
+          <t>63878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89599</t>
+          <t>92356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98930</t>
+          <t>97545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>133151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167903</t>
+          <t>168025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216561</t>
+          <t>215036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376344</t>
+          <t>373587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404168</t>
+          <t>402065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566542</t>
+          <t>566360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>600581</t>
+          <t>601966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>948893</t>
+          <t>950418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>997551</t>
+          <t>997429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211121</t>
+          <t>194169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354773</t>
+          <t>357103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289001</t>
+          <t>292107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>465336</t>
+          <t>462981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544740</t>
+          <t>542510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>787183</t>
+          <t>786688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1778602</t>
+          <t>1776272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1922254</t>
+          <t>1939206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1658936</t>
+          <t>1661291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1835271</t>
+          <t>1832165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3470465</t>
+          <t>3470960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3712908</t>
+          <t>3715138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114064</t>
+          <t>115623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162703</t>
+          <t>161523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122120</t>
+          <t>122508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156962</t>
+          <t>159158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>247445</t>
+          <t>250699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307718</t>
+          <t>306274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>456737</t>
+          <t>457917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505376</t>
+          <t>503817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474250</t>
+          <t>472054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>509092</t>
+          <t>508704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>942935</t>
+          <t>944379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1003208</t>
+          <t>999954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>394760</t>
+          <t>405391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>577128</t>
+          <t>577854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>525812</t>
+          <t>521253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>724648</t>
+          <t>725786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1146509</t>
+          <t>1146510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>983555</t>
+          <t>985721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1260442</t>
+          <t>1263603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2641630</t>
+          <t>2640904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2823998</t>
+          <t>2813367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2730348</t>
+          <t>2729210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2929184</t>
+          <t>2933743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5413312</t>
+          <t>5410152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5690199</t>
+          <t>5688034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6673754</t>
+          <t>6673755</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6673754</t>
+          <t>6673755</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6673754</t>
+          <t>6673755</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/Predimed_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Predimed_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63878</t>
+          <t>69757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92356</t>
+          <t>102634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>120669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97545</t>
+          <t>106326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>138027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>189628</t>
+          <t>205380</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168025</t>
+          <t>183767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215036</t>
+          <t>230092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>390715</t>
+          <t>432072</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373587</t>
+          <t>414149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402065</t>
+          <t>447026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>585111</t>
+          <t>642015</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566360</t>
+          <t>624657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601966</t>
+          <t>656358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>975826</t>
+          <t>1074087</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950418</t>
+          <t>1049375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>997429</t>
+          <t>1095700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>465943</t>
+          <t>516783</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>465943</t>
+          <t>516783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>465943</t>
+          <t>516783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>699511</t>
+          <t>762684</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>699511</t>
+          <t>762684</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>699511</t>
+          <t>762684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1165454</t>
+          <t>1279467</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1165454</t>
+          <t>1279467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1165454</t>
+          <t>1279467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>301946</t>
+          <t>334435</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194169</t>
+          <t>299888</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>357103</t>
+          <t>374562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>378592</t>
+          <t>384726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>292107</t>
+          <t>352146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>462981</t>
+          <t>416269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>680538</t>
+          <t>719162</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>542510</t>
+          <t>671088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>786688</t>
+          <t>773210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1831429</t>
+          <t>1733489</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1776272</t>
+          <t>1693362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1939206</t>
+          <t>1768036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1745680</t>
+          <t>1655562</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1661291</t>
+          <t>1624019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1832165</t>
+          <t>1688142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3577110</t>
+          <t>3389050</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3470960</t>
+          <t>3335002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3715138</t>
+          <t>3437124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2133375</t>
+          <t>2067924</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2133375</t>
+          <t>2067924</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2133375</t>
+          <t>2067924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2124272</t>
+          <t>2040288</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2124272</t>
+          <t>2040288</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2124272</t>
+          <t>2040288</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4257648</t>
+          <t>4108212</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4257648</t>
+          <t>4108212</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4257648</t>
+          <t>4108212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136905</t>
+          <t>155776</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115623</t>
+          <t>130856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161523</t>
+          <t>182598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>139438</t>
+          <t>157666</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122508</t>
+          <t>138623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159158</t>
+          <t>177900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>276344</t>
+          <t>313442</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250699</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306274</t>
+          <t>347514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>482535</t>
+          <t>526705</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457917</t>
+          <t>499883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503817</t>
+          <t>551625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>491774</t>
+          <t>545700</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>472054</t>
+          <t>525466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>508704</t>
+          <t>564743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>974309</t>
+          <t>1072404</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>944379</t>
+          <t>1038332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999954</t>
+          <t>1103637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>619440</t>
+          <t>682481</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>619440</t>
+          <t>682481</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>619440</t>
+          <t>682481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>631212</t>
+          <t>703366</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>631212</t>
+          <t>703366</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>631212</t>
+          <t>703366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1250653</t>
+          <t>1385846</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1250653</t>
+          <t>1385846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1250653</t>
+          <t>1385846</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>514079</t>
+          <t>574923</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405391</t>
+          <t>531634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>577854</t>
+          <t>625101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>632430</t>
+          <t>663061</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>521253</t>
+          <t>623319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>725786</t>
+          <t>710245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1146510</t>
+          <t>1237984</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>985721</t>
+          <t>1178868</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1263603</t>
+          <t>1302760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2704679</t>
+          <t>2692265</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2640904</t>
+          <t>2642087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2813367</t>
+          <t>2735554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2822566</t>
+          <t>2843277</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2729210</t>
+          <t>2796093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2933743</t>
+          <t>2883019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5527245</t>
+          <t>5535542</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5410152</t>
+          <t>5470766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5688034</t>
+          <t>5594658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3218758</t>
+          <t>3267188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3218758</t>
+          <t>3267188</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3218758</t>
+          <t>3267188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3454996</t>
+          <t>3506338</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3454996</t>
+          <t>3506338</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3454996</t>
+          <t>3506338</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6673755</t>
+          <t>6773526</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6673755</t>
+          <t>6773526</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6673755</t>
+          <t>6773526</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
